--- a/data/trans_orig/IP07KS_C04_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C04_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse solo/a en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse solo/a, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4164</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3885</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6978</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2987</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6298</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11496</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7171</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17558</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6114</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2622</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10730</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>25126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30067</t>
+          <t>27748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48597</t>
+          <t>49867</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41060</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54624</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4572</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>15,64%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4611</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13322</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8380</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10325</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6291</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15526</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35,4%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>24184</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17741</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12196</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23093</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>16116</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20706</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>33776</t>
+          <t>34886</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41281</t>
+          <t>41998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4459</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4370</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4499</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2742</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>39,18%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20106</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14439</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>23721</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>53,53%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>8367</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5172</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11179</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>35,55%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>76,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5518</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5511</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4854</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1660</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5533</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6148</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1660</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6013</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>355</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>21545</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>12426</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>34900</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>38397</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>16272</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>57430</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>57,18%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>24,23%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>35978</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37118</t>
+          <t>25150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95393</t>
+          <t>49685</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43282</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>30827</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>51730</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>62,35%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>74,52%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>24444</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>8323</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>43768</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>36,4%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>65,17%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>68815</t>
+          <t>67938</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90891</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,107 +3448,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>4452</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3561,107 +3561,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>4875</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5232</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>7054</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6003</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6440</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12997</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>21,98%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2205</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>6391</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>21323</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>11504</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>29761</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>19,45%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>50,32%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>9761</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>5487</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>14143</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>39,61%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20665</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>41460</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>31380</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>22779</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>43640</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>53,06%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>38,52%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>73,79%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>21694</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>17127</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>26604</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>47,96%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>74,5%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>54468</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>44114</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>69217</t>
+          <t>66389</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4243,107 +4243,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>3502</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>3758</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>3989</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3613</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>9505</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4230</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4967</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>14,02%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>3638</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>8285</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>16652</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>11474</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>22306</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>61,08%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>12620</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>8222</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>17376</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>57,58%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36810</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>14887</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>10039</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>20664</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>40,76%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>56,58%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>15419</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>10885</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>20148</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>66,77%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>3159</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>8442</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1544</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>9984</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>12090</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>28696</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>5111</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>16446</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38998</t>
+          <t>40633</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>89486</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>73063</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>105915</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>39,95%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>80657</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>57560</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>125630</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>38,92%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>60,62%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>87202</t>
+          <t>60315</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>70769</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>106577</t>
+          <t>73997</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>167860</t>
+          <t>149801</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>140372</t>
+          <t>130601</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>229700</t>
+          <t>172391</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>153039</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>135619</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>171327</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>57,72%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>51,15%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>64,62%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>109179</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>68288</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>129449</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>52,68%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>62,46%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>158087</t>
+          <t>114765</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>139070</t>
+          <t>102296</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>176395</t>
+          <t>126734</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>267266</t>
+          <t>267804</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>215341</t>
+          <t>243368</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>294920</t>
+          <t>289252</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,99%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
